--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M17B7_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M17B7_IN_Piura.xlsx
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>13.75</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>37.86</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>42.58</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>5.82</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1925,11 +1925,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>258.8372</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1950,11 +1950,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>133.5713</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>51.6</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1975,11 +1975,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>125.2659</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>48.4</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>258.9687</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2277,6 +2277,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2516,6 +2517,7 @@
       <c r="F16" s="17" t="inlineStr"/>
       <c r="G16" s="17" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -2560,6 +2562,7 @@
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -3014,11 +3017,11 @@
       </c>
       <c r="B19" s="33">
         <f>SUM(B10:B18)</f>
-        <v/>
+        <v>875.24</v>
       </c>
       <c r="C19" s="23">
         <f>SUM(C10:C18)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
@@ -3028,19 +3031,19 @@
       <c r="E19" s="17" t="inlineStr"/>
       <c r="F19" s="17">
         <f>ROUND(AVERAGE(F10:F18),2)</f>
-        <v/>
+        <v>22.85</v>
       </c>
       <c r="G19" s="22">
         <f>ROUND(AVERAGE(G10:G18),4)</f>
-        <v/>
+        <v>0.451</v>
       </c>
       <c r="H19" s="23">
         <f>ROUND(AVERAGE(H10:H18),2)</f>
-        <v/>
+        <v>29.59</v>
       </c>
       <c r="I19" s="23">
         <f>ROUND(AVERAGE(I10:I18),2)</f>
-        <v/>
+        <v>69.38</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
